--- a/data/trans_dic/IMC_inf_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_R2-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad declarado</t>
+          <t>Población con sobrepeso u obesidad declarado (tasa de respuesta: 79,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,27; 64,49</t>
+          <t>36,43; 64,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,96; 64,46</t>
+          <t>36,85; 63,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32,09; 60,05</t>
+          <t>32,87; 59,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,42; 52,26</t>
+          <t>21,15; 51,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>37,71; 62,47</t>
+          <t>35,91; 62,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,83; 62,75</t>
+          <t>31,86; 62,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,21; 64,3</t>
+          <t>35,78; 63,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,01; 50,76</t>
+          <t>17,92; 50,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>40,15; 58,96</t>
+          <t>40,45; 59,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38,11; 57,8</t>
+          <t>38,08; 58,61</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38,9; 57,88</t>
+          <t>38,51; 57,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,34; 46,86</t>
+          <t>23,58; 46,19</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>39,06; 49,91</t>
+          <t>38,86; 49,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,42; 52,24</t>
+          <t>40,11; 51,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,72; 46,26</t>
+          <t>34,42; 46,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32,66; 46,68</t>
+          <t>32,13; 45,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,46; 50,32</t>
+          <t>40,26; 50,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,54; 65,86</t>
+          <t>55,17; 66,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,85; 54,77</t>
+          <t>43,75; 54,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,39; 53,29</t>
+          <t>40,7; 53,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>41,04; 48,0</t>
+          <t>41,33; 48,27</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49,88; 57,74</t>
+          <t>49,57; 57,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41,17; 49,17</t>
+          <t>41,39; 49,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,42; 48,03</t>
+          <t>38,82; 48,04</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35,21; 49,85</t>
+          <t>35,3; 49,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44,35; 59,1</t>
+          <t>45,59; 59,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,84; 44,75</t>
+          <t>32,86; 45,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28,31; 42,82</t>
+          <t>29,01; 42,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>43,8; 57,9</t>
+          <t>43,75; 57,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,6; 56,33</t>
+          <t>42,38; 56,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,22; 56,11</t>
+          <t>43,92; 56,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33,98; 48,61</t>
+          <t>35,19; 48,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>41,36; 51,35</t>
+          <t>41,76; 51,31</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46,27; 56,02</t>
+          <t>45,5; 55,48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39,84; 48,98</t>
+          <t>40,35; 48,94</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>34,6; 44,12</t>
+          <t>34,39; 44,07</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,25; 21,93</t>
+          <t>13,06; 22,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,77; 33,48</t>
+          <t>21,38; 32,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,63; 27,6</t>
+          <t>16,52; 27,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,66; 22,22</t>
+          <t>11,66; 22,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>36,06; 47,55</t>
+          <t>36,02; 47,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,22; 44,34</t>
+          <t>31,36; 44,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,23; 37,89</t>
+          <t>25,77; 38,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26,18; 39,49</t>
+          <t>25,62; 39,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,97; 33,43</t>
+          <t>26,29; 33,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28,56; 36,82</t>
+          <t>28,13; 36,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,96; 30,25</t>
+          <t>22,27; 30,7</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,5; 30,35</t>
+          <t>20,56; 30,02</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>32,29; 38,59</t>
+          <t>32,38; 38,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38,97; 45,71</t>
+          <t>38,24; 45,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,75; 38,2</t>
+          <t>31,34; 38,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23,63; 32,22</t>
+          <t>24,07; 32,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>42,26; 48,48</t>
+          <t>42,27; 48,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,95; 54,25</t>
+          <t>46,84; 53,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,18; 48,25</t>
+          <t>41,28; 48,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,86; 42,9</t>
+          <t>35,21; 43,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,08; 42,61</t>
+          <t>38,2; 42,75</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43,86; 49,11</t>
+          <t>43,85; 48,69</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37,54; 42,22</t>
+          <t>37,7; 42,69</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,66; 36,92</t>
+          <t>30,95; 36,93</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población con sobrepeso u obesidad declarado (tasa de respuesta: 79,86%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>15716</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15924</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15434</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9171</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>20551</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>12868</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>15938</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>6608</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>36267</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>28792</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>31372</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>15779</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>11452; 20351</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11799; 20454</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>11068; 19970</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5410; 13042</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>14728; 25429</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>8811; 17166</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>11377; 20042</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>3495; 9905</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>29306; 43124</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>22723; 34974</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>25207; 37928</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>10628; 20822</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>102632</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>91853</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>74694</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>54147</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>103269</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>137547</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>110830</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>79687</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>205901</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>229401</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>185525</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>133834</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>89923; 114520</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>80182; 103800</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>63552; 85060</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>44580; 63796</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>92270; 115532</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>124794; 149365</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>98997; 123426</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>69041; 90629</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>190345; 222327</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>211236; 246020</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>170081; 202545</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>119717; 148157</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>52162</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>72140</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>66392</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>57763</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>67217</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>69383</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>86082</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>77808</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>119378</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>141523</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>152474</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>135571</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>43923; 61749</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>62743; 81658</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>56143; 77354</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>47135; 69828</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>58216; 76459</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>59606; 80007</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>75489; 97457</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>65326; 90881</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>107533; 132136</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>126633; 154399</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>138294; 167735</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>119712; 153426</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>33215</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>42249</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>33346</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>41921</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>83953</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>61192</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>48322</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>90499</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>117168</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>103441</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>81667</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>132420</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>24916; 42778</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>33664; 51323</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>25651; 42488</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>28976; 55888</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>72837; 95472</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>50827; 71473</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>39690; 59071</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>71240; 109332</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>103335; 132014</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>89909; 118033</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>68881; 94937</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>108258; 158086</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>723</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>721</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>203724</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>222166</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>189866</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>163002</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>274990</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>280991</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>261173</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>254601</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>478715</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>503157</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>451038</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>417604</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>187155; 221822</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>201556; 239622</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>170642; 208172</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>138492; 185800</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>255946; 295496</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>260698; 298687</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>241033; 280406</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>229878; 282178</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>452143; 506013</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>475219; 527639</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>425364; 481685</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>380194; 453554</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IMC_inf_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_R2-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad declarado (tasa de respuesta: 79,86%)</t>
+          <t>Población con sobrepeso u obesidad declarado por los/as progenitores/as (tasa de respuesta: 79,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,43; 64,74</t>
+          <t>37,19; 64,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>36,85; 63,89</t>
+          <t>35,94; 62,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32,87; 59,32</t>
+          <t>32,3; 58,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,15; 51,0</t>
+          <t>22,17; 52,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,91; 62,0</t>
+          <t>38,08; 62,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,86; 62,07</t>
+          <t>31,63; 62,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,78; 63,04</t>
+          <t>36,77; 63,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,92; 50,79</t>
+          <t>19,73; 52,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>40,45; 59,52</t>
+          <t>40,86; 59,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38,08; 58,61</t>
+          <t>37,36; 57,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38,51; 57,94</t>
+          <t>38,37; 57,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23,58; 46,19</t>
+          <t>24,32; 46,4</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,86; 49,49</t>
+          <t>38,41; 49,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,11; 51,92</t>
+          <t>40,28; 52,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,42; 46,07</t>
+          <t>33,91; 46,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32,13; 45,97</t>
+          <t>32,84; 46,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,26; 50,41</t>
+          <t>39,97; 50,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,17; 66,03</t>
+          <t>55,18; 66,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,75; 54,55</t>
+          <t>43,87; 54,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,7; 53,43</t>
+          <t>40,55; 53,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>41,33; 48,27</t>
+          <t>41,29; 48,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49,57; 57,74</t>
+          <t>50,05; 58,46</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41,39; 49,3</t>
+          <t>41,4; 49,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,82; 48,04</t>
+          <t>39,19; 47,94</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35,3; 49,62</t>
+          <t>34,22; 49,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45,59; 59,33</t>
+          <t>45,73; 59,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,86; 45,28</t>
+          <t>32,64; 45,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29,01; 42,97</t>
+          <t>29,39; 43,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>43,75; 57,46</t>
+          <t>44,23; 58,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,38; 56,88</t>
+          <t>42,96; 56,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43,92; 56,7</t>
+          <t>44,0; 56,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,19; 48,96</t>
+          <t>34,68; 48,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>41,76; 51,31</t>
+          <t>41,09; 51,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45,5; 55,48</t>
+          <t>45,84; 55,65</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40,35; 48,94</t>
+          <t>40,26; 49,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>34,39; 44,07</t>
+          <t>34,52; 44,21</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,06; 22,42</t>
+          <t>12,57; 22,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,38; 32,59</t>
+          <t>20,9; 32,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,52; 27,37</t>
+          <t>15,87; 27,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,66; 22,49</t>
+          <t>11,04; 22,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>36,02; 47,22</t>
+          <t>35,81; 46,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,36; 44,09</t>
+          <t>31,34; 43,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,77; 38,36</t>
+          <t>25,49; 38,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,62; 39,31</t>
+          <t>25,44; 39,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26,29; 33,59</t>
+          <t>26,4; 33,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28,13; 36,94</t>
+          <t>28,06; 36,81</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22,27; 30,7</t>
+          <t>21,77; 30,32</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,56; 30,02</t>
+          <t>20,36; 30,0</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>32,38; 38,37</t>
+          <t>32,24; 38,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38,24; 45,47</t>
+          <t>38,77; 45,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,34; 38,24</t>
+          <t>31,33; 38,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,07; 32,29</t>
+          <t>23,7; 32,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>42,27; 48,81</t>
+          <t>41,92; 48,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,84; 53,66</t>
+          <t>47,09; 53,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,28; 48,02</t>
+          <t>41,36; 48,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>35,21; 43,22</t>
+          <t>35,05; 42,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,2; 42,75</t>
+          <t>38,05; 42,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43,85; 48,69</t>
+          <t>43,8; 48,59</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37,7; 42,69</t>
+          <t>37,46; 42,29</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,95; 36,93</t>
+          <t>30,92; 36,9</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad declarado (tasa de respuesta: 79,86%)</t>
+          <t>Población con sobrepeso u obesidad declarado por los/as progenitores/as (tasa de respuesta: 79,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11452; 20351</t>
+          <t>11691; 20363</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11799; 20454</t>
+          <t>11505; 19854</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11068; 19970</t>
+          <t>10873; 19854</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5410; 13042</t>
+          <t>5671; 13345</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14728; 25429</t>
+          <t>15618; 25444</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8811; 17166</t>
+          <t>8747; 17420</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11377; 20042</t>
+          <t>11690; 20324</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3495; 9905</t>
+          <t>3848; 10310</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29306; 43124</t>
+          <t>29604; 43012</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22723; 34974</t>
+          <t>22292; 34465</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25207; 37928</t>
+          <t>25116; 37509</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10628; 20822</t>
+          <t>10961; 20915</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>89923; 114520</t>
+          <t>88887; 113642</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>80182; 103800</t>
+          <t>80529; 105237</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63552; 85060</t>
+          <t>62613; 84950</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>44580; 63796</t>
+          <t>45573; 64067</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>92270; 115532</t>
+          <t>91606; 115245</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>124794; 149365</t>
+          <t>124806; 150561</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>98997; 123426</t>
+          <t>99249; 123313</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>69041; 90629</t>
+          <t>68781; 90662</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>190345; 222327</t>
+          <t>190153; 223668</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>211236; 246020</t>
+          <t>213274; 249113</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>170081; 202545</t>
+          <t>170110; 202651</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>119717; 148157</t>
+          <t>120847; 147842</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>43923; 61749</t>
+          <t>42584; 61749</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>62743; 81658</t>
+          <t>62944; 82507</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56143; 77354</t>
+          <t>55769; 77421</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47135; 69828</t>
+          <t>47755; 69920</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>58216; 76459</t>
+          <t>58848; 77642</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>59606; 80007</t>
+          <t>60430; 78874</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>75489; 97457</t>
+          <t>75619; 97800</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>65326; 90881</t>
+          <t>64378; 89225</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>107533; 132136</t>
+          <t>105805; 132723</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>126633; 154399</t>
+          <t>127570; 154877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>138294; 167735</t>
+          <t>137995; 168035</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>119712; 153426</t>
+          <t>120175; 153888</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24916; 42778</t>
+          <t>23976; 42038</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33664; 51323</t>
+          <t>32915; 51565</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25651; 42488</t>
+          <t>24647; 42354</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28976; 55888</t>
+          <t>27434; 55375</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>72837; 95472</t>
+          <t>72408; 94866</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50827; 71473</t>
+          <t>50806; 70590</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39690; 59071</t>
+          <t>39250; 58784</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>71240; 109332</t>
+          <t>70745; 108911</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>103335; 132014</t>
+          <t>103745; 132261</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>89909; 118033</t>
+          <t>89685; 117632</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>68881; 94937</t>
+          <t>67341; 93782</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>108258; 158086</t>
+          <t>107207; 157984</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>187155; 221822</t>
+          <t>186354; 221172</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>201556; 239622</t>
+          <t>204318; 242337</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>170642; 208172</t>
+          <t>170586; 208083</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>138492; 185800</t>
+          <t>136345; 185752</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>255946; 295496</t>
+          <t>253811; 293625</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>260698; 298687</t>
+          <t>262113; 300282</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>241033; 280406</t>
+          <t>241538; 281183</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>229878; 282178</t>
+          <t>228801; 279715</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>452143; 506013</t>
+          <t>450305; 505438</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>475219; 527639</t>
+          <t>474635; 526569</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>425364; 481685</t>
+          <t>422726; 477154</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>380194; 453554</t>
+          <t>379725; 453220</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IMC_inf_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_R2-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>50,1%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>46,53%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>50,13%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>34,53%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>50,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>49,74%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>45,84%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>35,86%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>50,1%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>46,53%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>50,13%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,93%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,19; 64,78</t>
+          <t>37,71; 62,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,94; 62,02</t>
+          <t>30,83; 62,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32,3; 58,97</t>
+          <t>36,21; 64,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,17; 52,18</t>
+          <t>19,03; 51,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,08; 62,03</t>
+          <t>37,27; 64,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,63; 62,99</t>
+          <t>35,96; 64,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,77; 63,92</t>
+          <t>32,09; 60,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,73; 52,87</t>
+          <t>21,34; 51,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>40,86; 59,37</t>
+          <t>40,15; 58,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37,36; 57,76</t>
+          <t>38,11; 57,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38,37; 57,3</t>
+          <t>38,9; 57,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,32; 46,4</t>
+          <t>24,38; 47,32</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>45,06%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60,81%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>48,98%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>47,02%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>44,35%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>45,95%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>40,46%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>39,02%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>45,06%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>60,81%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>48,98%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>42,44%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,41; 49,11</t>
+          <t>39,46; 50,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,28; 52,64</t>
+          <t>54,54; 65,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,91; 46,01</t>
+          <t>43,85; 54,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32,84; 46,17</t>
+          <t>40,27; 53,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,97; 50,29</t>
+          <t>39,06; 49,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,18; 66,56</t>
+          <t>40,42; 52,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,87; 54,5</t>
+          <t>34,72; 46,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,55; 53,45</t>
+          <t>31,36; 44,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>41,29; 48,56</t>
+          <t>41,04; 48,0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50,05; 58,46</t>
+          <t>49,88; 57,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41,4; 49,32</t>
+          <t>41,17; 49,17</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,19; 47,94</t>
+          <t>37,67; 47,2</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>50,52%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>49,33%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>50,08%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>42,11%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>41,92%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>52,41%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>38,86%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>35,55%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>50,52%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>49,33%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>50,08%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,6%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34,22; 49,62</t>
+          <t>43,8; 57,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45,73; 59,95</t>
+          <t>42,6; 56,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,64; 45,31</t>
+          <t>44,22; 56,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29,39; 43,03</t>
+          <t>34,24; 48,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>44,23; 58,35</t>
+          <t>35,21; 49,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,96; 56,07</t>
+          <t>44,35; 59,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,0; 56,9</t>
+          <t>32,84; 44,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34,68; 48,07</t>
+          <t>28,08; 41,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>41,09; 51,54</t>
+          <t>41,36; 51,35</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45,84; 55,65</t>
+          <t>46,27; 56,02</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40,26; 49,03</t>
+          <t>39,84; 48,98</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>34,52; 44,21</t>
+          <t>33,96; 43,51</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>41,52%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>37,75%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>31,38%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>33,57%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>17,41%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>26,83%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>21,48%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>16,87%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>41,52%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>37,75%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>31,38%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,57; 22,03</t>
+          <t>36,06; 47,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,9; 32,75</t>
+          <t>32,22; 44,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,87; 27,28</t>
+          <t>25,23; 37,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,04; 22,28</t>
+          <t>26,99; 40,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,81; 46,92</t>
+          <t>13,25; 21,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,34; 43,55</t>
+          <t>21,77; 33,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,49; 38,17</t>
+          <t>16,63; 27,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,44; 39,16</t>
+          <t>14,09; 23,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26,4; 33,65</t>
+          <t>25,97; 33,43</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28,06; 36,81</t>
+          <t>28,56; 36,82</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,77; 30,32</t>
+          <t>21,96; 30,25</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,36; 30,0</t>
+          <t>22,73; 31,2</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>45,42%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>50,48%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>44,73%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>39,37%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>35,24%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>42,15%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>34,88%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>28,33%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>45,42%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>50,48%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>44,73%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,25%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>32,24; 38,26</t>
+          <t>42,26; 48,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38,77; 45,98</t>
+          <t>46,95; 54,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,33; 38,22</t>
+          <t>41,18; 48,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23,7; 32,28</t>
+          <t>35,32; 43,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>41,92; 48,5</t>
+          <t>32,29; 38,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,09; 53,95</t>
+          <t>38,97; 45,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,36; 48,15</t>
+          <t>31,75; 38,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>35,05; 42,85</t>
+          <t>25,56; 31,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,05; 42,71</t>
+          <t>38,08; 42,61</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43,8; 48,59</t>
+          <t>43,86; 49,11</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37,46; 42,29</t>
+          <t>37,54; 42,22</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,92; 36,9</t>
+          <t>31,8; 36,74</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>20551</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12868</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15938</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5565</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>15716</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>15924</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>15434</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9171</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>20551</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>12868</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>15938</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15779</t>
+          <t>14235</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11691; 20363</t>
+          <t>15469; 25623</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11505; 19854</t>
+          <t>8526; 17352</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10873; 19854</t>
+          <t>11512; 20445</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5671; 13345</t>
+          <t>3067; 8358</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15618; 25444</t>
+          <t>11715; 20272</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8747; 17420</t>
+          <t>11513; 20636</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11690; 20324</t>
+          <t>10804; 20217</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3848; 10310</t>
+          <t>5258; 12650</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29604; 43012</t>
+          <t>29089; 42715</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22292; 34465</t>
+          <t>22741; 34489</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25116; 37509</t>
+          <t>25464; 37887</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10961; 20915</t>
+          <t>9937; 19284</t>
         </is>
       </c>
     </row>
@@ -1722,37 +1722,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>86</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>103269</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>137547</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>110830</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>69419</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>102632</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>91853</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>74694</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>54147</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>103269</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>137547</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>110830</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>79687</t>
+          <t>47980</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>133834</t>
+          <t>117400</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>88887; 113642</t>
+          <t>90440; 115313</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>80529; 105237</t>
+          <t>123364; 148974</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62613; 84950</t>
+          <t>99205; 123926</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45573; 64067</t>
+          <t>59448; 79434</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>91606; 115245</t>
+          <t>90376; 115494</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>124806; 150561</t>
+          <t>80803; 104427</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>99249; 123313</t>
+          <t>64099; 85400</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>68781; 90662</t>
+          <t>40442; 57068</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>190153; 223668</t>
+          <t>189029; 221052</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>213274; 249113</t>
+          <t>212560; 246050</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>170110; 202651</t>
+          <t>169174; 202026</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>120847; 147842</t>
+          <t>104209; 130548</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>102</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>77</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>67217</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>69383</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>86082</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>75039</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>52162</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>72140</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>66392</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>57763</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>67217</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>69383</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>86082</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>77808</t>
+          <t>56769</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>135571</t>
+          <t>131808</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>42584; 61749</t>
+          <t>58282; 77049</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>62944; 82507</t>
+          <t>59927; 79240</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>55769; 77421</t>
+          <t>76008; 96439</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47755; 69920</t>
+          <t>61013; 86943</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>58848; 77642</t>
+          <t>43811; 62034</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>60430; 78874</t>
+          <t>61037; 81347</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>75619; 97800</t>
+          <t>56101; 76450</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>64378; 89225</t>
+          <t>45861; 67079</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>105805; 132723</t>
+          <t>106491; 132239</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>127570; 154877</t>
+          <t>128778; 155889</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>137995; 168035</t>
+          <t>136544; 167875</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>120175; 153888</t>
+          <t>115981; 148582</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>56</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>83953</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>61192</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>48322</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>89095</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>33215</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>42249</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>33346</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>41921</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>83953</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>61192</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>48322</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>90499</t>
+          <t>42084</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>132420</t>
+          <t>131179</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23976; 42038</t>
+          <t>72916; 96158</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32915; 51565</t>
+          <t>52231; 71879</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24647; 42354</t>
+          <t>38856; 58353</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27434; 55375</t>
+          <t>71630; 106746</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>72408; 94866</t>
+          <t>25289; 41840</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50806; 70590</t>
+          <t>34281; 52724</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39250; 58784</t>
+          <t>25813; 42853</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>70745; 108911</t>
+          <t>32115; 52933</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>103745; 132261</t>
+          <t>102052; 131362</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>89685; 117632</t>
+          <t>91259; 117673</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>67341; 93782</t>
+          <t>67921; 93549</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>107207; 157984</t>
+          <t>112158; 153918</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>309</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>317</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>283</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>234</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>316</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>274990</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>280991</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>261173</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>239119</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>203724</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>222166</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>189866</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>163002</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>274990</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>280991</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>261173</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>254601</t>
+          <t>155504</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>417604</t>
+          <t>394622</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>186354; 221172</t>
+          <t>255865; 293526</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>204318; 242337</t>
+          <t>261343; 301978</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>170586; 208083</t>
+          <t>240456; 281764</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>136345; 185752</t>
+          <t>214496; 262239</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>253811; 293625</t>
+          <t>186635; 223096</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>262113; 300282</t>
+          <t>205399; 240883</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>241538; 281183</t>
+          <t>172831; 207961</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>228801; 279715</t>
+          <t>139280; 173325</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>450305; 505438</t>
+          <t>450692; 504253</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>474635; 526569</t>
+          <t>475291; 532153</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>422726; 477154</t>
+          <t>423582; 476396</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>379725; 453220</t>
+          <t>366438; 423257</t>
         </is>
       </c>
     </row>
